--- a/test_file.xlsx
+++ b/test_file.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="test file" sheetId="1" r:id="rId1"/>
@@ -1175,75 +1175,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>7</v>
       </c>
